--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78D6292F-56EC-4514-8DAF-7793247EFC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D60CCF-F00F-438E-8B16-464C1CD27ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>160673</v>
+            <v>191605</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>274103</v>
+            <v>329052</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.63861154599099867</v>
+            <v>-0.56433810658742678</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.64619018188239452</v>
+            <v>-0.604052622285008</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>18792</v>
+            <v>23917</v>
           </cell>
         </row>
       </sheetData>
@@ -413,7 +413,7 @@
             <v>8218</v>
           </cell>
           <cell r="I6">
-            <v>3937</v>
+            <v>8000</v>
           </cell>
         </row>
         <row r="7">
@@ -436,7 +436,7 @@
             <v>2340</v>
           </cell>
           <cell r="I7">
-            <v>855</v>
+            <v>1278</v>
           </cell>
         </row>
         <row r="8">
@@ -459,7 +459,7 @@
             <v>21670</v>
           </cell>
           <cell r="I8">
-            <v>7207</v>
+            <v>11358</v>
           </cell>
         </row>
         <row r="9">
@@ -482,7 +482,7 @@
             <v>2832</v>
           </cell>
           <cell r="I9">
-            <v>1321</v>
+            <v>1751</v>
           </cell>
         </row>
         <row r="10">
@@ -560,7 +560,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>12871</v>
+            <v>14984</v>
           </cell>
         </row>
       </sheetData>
@@ -619,34 +619,51 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="D4">
+            <v>14984</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="24">
+          <cell r="C24">
+            <v>22468</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>129037</v>
+            <v>155557</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8"/>
+      <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9">
+        <row r="3">
+          <cell r="C3">
+            <v>10567</v>
+          </cell>
+        </row>
         <row r="39">
           <cell r="G39">
-            <v>16029</v>
+            <v>17938</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1012,7 +1029,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>160673</v>
+        <v>191605</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,7 +1231,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>274103</v>
+        <v>329052</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1261,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.36191901744518989</v>
+        <v>-0.23400392016276592</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1337,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>129037</v>
+        <v>155557</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1364,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.63861154599099867</v>
+        <v>-0.56433810658742678</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1440,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>16029</v>
+        <v>17938</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1467,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.64619018188239452</v>
+        <v>-0.604052622285008</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1542,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>18792</v>
+        <v>23917</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1549,7 +1566,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.68194973343488197</v>
+        <v>-0.59521029025979522</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1642,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>19201</v>
+        <v>27415</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,7 +1669,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.4511490967299337</v>
+        <v>-0.21635604847930481</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +1745,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
-        <v>2176</v>
+        <v>3029</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1755,7 +1772,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.57927300850734731</v>
+        <v>-0.41434648105181748</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1951,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>12871</v>
+        <v>14984</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1961,7 +1978,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.67698137830647998</v>
+        <v>-0.62395221603172213</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D60CCF-F00F-438E-8B16-464C1CD27ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF22A6A-83D1-4BB0-838D-B04176C7A306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>191605</v>
+            <v>227601</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>329052</v>
+            <v>197759</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.56433810658742678</v>
+            <v>-0.49638295071682831</v>
           </cell>
         </row>
         <row r="9">
@@ -560,7 +560,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>14984</v>
+            <v>20716</v>
           </cell>
         </row>
       </sheetData>
@@ -585,7 +585,7 @@
             <v>45389</v>
           </cell>
           <cell r="K13">
-            <v>1776</v>
+            <v>7382</v>
           </cell>
         </row>
       </sheetData>
@@ -622,14 +622,14 @@
       <sheetData sheetId="0">
         <row r="4">
           <cell r="D4">
-            <v>14984</v>
+            <v>20716</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1">
         <row r="24">
           <cell r="C24">
-            <v>22468</v>
+            <v>30500</v>
           </cell>
         </row>
       </sheetData>
@@ -641,7 +641,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>155557</v>
+            <v>179821</v>
           </cell>
         </row>
       </sheetData>
@@ -649,7 +649,7 @@
       <sheetData sheetId="9">
         <row r="3">
           <cell r="C3">
-            <v>10567</v>
+            <v>14554</v>
           </cell>
         </row>
         <row r="39">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>191605</v>
+        <v>227601</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Gelatina!$K$13</f>
-        <v>1776</v>
+        <v>7382</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.96087157681376545</v>
+        <v>-0.83736147524730664</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>329052</v>
+        <v>197759</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.23400392016276592</v>
+        <v>-0.53963927053313288</v>
       </c>
     </row>
   </sheetData>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>155557</v>
+        <v>179821</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.56433810658742678</v>
+        <v>-0.49638295071682831</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>14984</v>
+        <v>20716</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.62395221603172213</v>
+        <v>-0.48009837875821915</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF22A6A-83D1-4BB0-838D-B04176C7A306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D9CA24-9970-47C9-8671-577A1C547E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion Total Mensual" sheetId="1" r:id="rId1"/>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D9CA24-9970-47C9-8671-577A1C547E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DF99A3-67D8-47E0-A212-31B7E30F12A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion Total Mensual" sheetId="1" r:id="rId1"/>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>227601</v>
+            <v>245294</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>197759</v>
+            <v>210817</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.49638295071682831</v>
+            <v>-0.46810191032854515</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.604052622285008</v>
+            <v>-0.53871622814762499</v>
           </cell>
         </row>
         <row r="7">
@@ -585,7 +585,7 @@
             <v>45389</v>
           </cell>
           <cell r="K13">
-            <v>7382</v>
+            <v>11882</v>
           </cell>
         </row>
       </sheetData>
@@ -619,20 +619,8 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="D4">
-            <v>20716</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1">
-        <row r="24">
-          <cell r="C24">
-            <v>30500</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3" refreshError="1"/>
       <sheetData sheetId="4" refreshError="1"/>
@@ -641,20 +629,15 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>179821</v>
+            <v>189919</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="8" refreshError="1"/>
       <sheetData sheetId="9">
-        <row r="3">
-          <cell r="C3">
-            <v>14554</v>
-          </cell>
-        </row>
         <row r="39">
           <cell r="G39">
-            <v>17938</v>
+            <v>22852</v>
           </cell>
         </row>
       </sheetData>
@@ -1029,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>227601</v>
+        <v>245294</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1128,7 +1111,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Gelatina!$K$13</f>
-        <v>7382</v>
+        <v>11882</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1155,7 +1138,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.83736147524730664</v>
+        <v>-0.73821851109299608</v>
       </c>
     </row>
   </sheetData>
@@ -1231,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>197759</v>
+        <v>210817</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1261,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.53963927053313288</v>
+        <v>-0.50924171388398742</v>
       </c>
     </row>
   </sheetData>
@@ -1337,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>179821</v>
+        <v>189919</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1364,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.49638295071682831</v>
+        <v>-0.46810191032854515</v>
       </c>
     </row>
   </sheetData>
@@ -1440,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>17938</v>
+        <v>22852</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1467,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.604052622285008</v>
+        <v>-0.53871622814762499</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36DF99A3-67D8-47E0-A212-31B7E30F12A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF220CC8-0D03-45CB-BC59-D2DFDED449CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,11 +205,11 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>245294</v>
+            <v>263174</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>210817</v>
+            <v>228697</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.46810191032854515</v>
+            <v>-0.42713389103761562</v>
           </cell>
         </row>
         <row r="9">
@@ -336,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.53871622814762499</v>
+            <v>-0.46693448702101359</v>
           </cell>
         </row>
         <row r="7">
@@ -413,7 +413,7 @@
             <v>8218</v>
           </cell>
           <cell r="I6">
-            <v>8000</v>
+            <v>10071</v>
           </cell>
         </row>
         <row r="7">
@@ -459,7 +459,7 @@
             <v>21670</v>
           </cell>
           <cell r="I8">
-            <v>11358</v>
+            <v>15500</v>
           </cell>
         </row>
         <row r="9">
@@ -619,34 +619,34 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>189919</v>
+            <v>204547</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="8"/>
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>22852</v>
+            <v>32231</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>245294</v>
+        <v>263174</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>210817</v>
+        <v>228697</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.50924171388398742</v>
+        <v>-0.46761908309162098</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>189919</v>
+        <v>204547</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.46810191032854515</v>
+        <v>-0.42713389103761562</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>22852</v>
+        <v>32231</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.53871622814762499</v>
+        <v>-0.46693448702101359</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>27415</v>
+        <v>33628</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.21635604847930481</v>
+        <v>-3.8760576263434716E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF220CC8-0D03-45CB-BC59-D2DFDED449CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4C5066-AFE1-4660-8560-DA32E487245D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>263174</v>
+            <v>286721</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>228697</v>
+            <v>249704</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.42713389103761562</v>
+            <v>-0.37407543291164763</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.46693448702101359</v>
+            <v>-0.42141974218612044</v>
           </cell>
         </row>
         <row r="7">
@@ -482,7 +482,7 @@
             <v>2832</v>
           </cell>
           <cell r="I9">
-            <v>1751</v>
+            <v>2207</v>
           </cell>
         </row>
         <row r="10">
@@ -505,7 +505,7 @@
             <v>5096</v>
           </cell>
           <cell r="I10">
-            <v>2032</v>
+            <v>5920</v>
           </cell>
         </row>
         <row r="11">
@@ -535,7 +535,7 @@
       <sheetData sheetId="9">
         <row r="15">
           <cell r="K15">
-            <v>6010</v>
+            <v>10493</v>
           </cell>
         </row>
       </sheetData>
@@ -629,7 +629,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>204547</v>
+            <v>223492</v>
           </cell>
         </row>
       </sheetData>
@@ -637,7 +637,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>32231</v>
+            <v>34293</v>
           </cell>
         </row>
       </sheetData>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>263174</v>
+        <v>286721</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>228697</v>
+        <v>249704</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.46761908309162098</v>
+        <v>-0.41871714768584689</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>204547</v>
+        <v>223492</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.42713389103761562</v>
+        <v>-0.37407543291164763</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>32231</v>
+        <v>34293</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.46693448702101359</v>
+        <v>-0.42141974218612044</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>33628</v>
+        <v>37516</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-3.8760576263434716E-2</v>
+        <v>7.2375943288360389E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
-        <v>3029</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.41434648105181748</v>
+        <v>-0.32617942768754832</v>
       </c>
     </row>
   </sheetData>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Frutas!$K$15</f>
-        <v>6010</v>
+        <v>10493</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF4C5066-AFE1-4660-8560-DA32E487245D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70959BF1-D0DB-4A64-AC9B-5B642B3DEA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>286721</v>
+            <v>317080</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>249704</v>
+            <v>272362</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.37407543291164763</v>
+            <v>-0.31880725594369558</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.42141974218612044</v>
+            <v>-0.35687797986932723</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>23917</v>
+            <v>26403</v>
           </cell>
         </row>
       </sheetData>
@@ -560,7 +560,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>20716</v>
+            <v>25681</v>
           </cell>
         </row>
       </sheetData>
@@ -629,7 +629,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>223492</v>
+            <v>243226</v>
           </cell>
         </row>
       </sheetData>
@@ -637,7 +637,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>34293</v>
+            <v>37217</v>
           </cell>
         </row>
       </sheetData>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>286721</v>
+        <v>317080</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>249704</v>
+        <v>272362</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.41871714768584689</v>
+        <v>-0.36597186980590074</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>223492</v>
+        <v>243226</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.37407543291164763</v>
+        <v>-0.31880725594369558</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>34293</v>
+        <v>37217</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.42141974218612044</v>
+        <v>-0.35687797986932723</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>23917</v>
+        <v>26403</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.59521029025979522</v>
+        <v>-0.55313531353135315</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>20716</v>
+        <v>25681</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.48009837875821915</v>
+        <v>-0.35549365055463533</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70959BF1-D0DB-4A64-AC9B-5B642B3DEA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5DC4E2-E420-407C-9FA4-2BE21BB4256D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>317080</v>
+            <v>359553</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>272362</v>
+            <v>305023</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.31880725594369558</v>
+            <v>-0.23156677187803695</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.35687797986932723</v>
+            <v>-0.3235255165106834</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>26403</v>
+            <v>34829</v>
           </cell>
         </row>
       </sheetData>
@@ -585,7 +585,7 @@
             <v>45389</v>
           </cell>
           <cell r="K13">
-            <v>11882</v>
+            <v>21107</v>
           </cell>
         </row>
       </sheetData>
@@ -629,7 +629,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>243226</v>
+            <v>274376</v>
           </cell>
         </row>
       </sheetData>
@@ -637,7 +637,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>37217</v>
+            <v>38728</v>
           </cell>
         </row>
       </sheetData>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>317080</v>
+        <v>359553</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Gelatina!$K$13</f>
-        <v>11882</v>
+        <v>21107</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.73821851109299608</v>
+        <v>-0.53497543457665953</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>272362</v>
+        <v>305023</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.36597186980590074</v>
+        <v>-0.2899407319809858</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>243226</v>
+        <v>274376</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.31880725594369558</v>
+        <v>-0.23156677187803695</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>37217</v>
+        <v>38728</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.35687797986932723</v>
+        <v>-0.3235255165106834</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>26403</v>
+        <v>34829</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.55313531353135315</v>
+        <v>-0.41052720656681052</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5DC4E2-E420-407C-9FA4-2BE21BB4256D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3CF515-3891-43A5-938C-4D8AF2A952A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
   </externalReferences>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -205,11 +205,11 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>359553</v>
+            <v>406700</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>305023</v>
+            <v>340405</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.23156677187803695</v>
+            <v>-0.13612596237596589</v>
           </cell>
         </row>
         <row r="9">
@@ -336,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.3235255165106834</v>
+            <v>-0.29474218612043085</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>34829</v>
+            <v>37239</v>
           </cell>
         </row>
       </sheetData>
@@ -413,7 +413,7 @@
             <v>8218</v>
           </cell>
           <cell r="I6">
-            <v>10071</v>
+            <v>15181</v>
           </cell>
         </row>
         <row r="7">
@@ -436,7 +436,7 @@
             <v>2340</v>
           </cell>
           <cell r="I7">
-            <v>1278</v>
+            <v>2134</v>
           </cell>
         </row>
         <row r="8">
@@ -459,7 +459,7 @@
             <v>21670</v>
           </cell>
           <cell r="I8">
-            <v>15500</v>
+            <v>22361</v>
           </cell>
         </row>
         <row r="9">
@@ -482,7 +482,7 @@
             <v>2832</v>
           </cell>
           <cell r="I9">
-            <v>2207</v>
+            <v>2655</v>
           </cell>
         </row>
         <row r="10">
@@ -585,7 +585,7 @@
             <v>45389</v>
           </cell>
           <cell r="K13">
-            <v>21107</v>
+            <v>27662</v>
           </cell>
         </row>
       </sheetData>
@@ -629,7 +629,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>274376</v>
+            <v>308454</v>
           </cell>
         </row>
       </sheetData>
@@ -637,7 +637,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>38728</v>
+            <v>40032</v>
           </cell>
         </row>
       </sheetData>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>359553</v>
+        <v>406700</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Gelatina!$K$13</f>
-        <v>21107</v>
+        <v>27662</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.53497543457665953</v>
+        <v>-0.39055718345854723</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>305023</v>
+        <v>340405</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.2899407319809858</v>
+        <v>-0.20757541191971582</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>274376</v>
+        <v>308454</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.23156677187803695</v>
+        <v>-0.13612596237596589</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>38728</v>
+        <v>40032</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.3235255165106834</v>
+        <v>-0.29474218612043085</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>34829</v>
+        <v>37239</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.41052720656681052</v>
+        <v>-0.36973851231276972</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>37516</v>
+        <v>49487</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>7.2375943288360389E-2</v>
+        <v>0.41456094214498057</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
-        <v>3485</v>
+        <v>4789</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.32617942768754832</v>
+        <v>-7.4052590873936577E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3CF515-3891-43A5-938C-4D8AF2A952A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140EF390-5777-495A-9C2E-3048105A656A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,11 +205,11 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>406700</v>
+            <v>438955</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="I12">
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>340405</v>
+            <v>371695</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-0.13612596237596589</v>
+            <v>-5.8701783178690355E-2</v>
           </cell>
         </row>
         <row r="9">
@@ -336,7 +336,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="5">
           <cell r="I5">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.29474218612043085</v>
+            <v>-0.21428571428571427</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>37239</v>
+            <v>39757</v>
           </cell>
         </row>
       </sheetData>
@@ -459,7 +459,7 @@
             <v>21670</v>
           </cell>
           <cell r="I8">
-            <v>22361</v>
+            <v>22642</v>
           </cell>
         </row>
         <row r="9">
@@ -505,7 +505,7 @@
             <v>5096</v>
           </cell>
           <cell r="I10">
-            <v>5920</v>
+            <v>7837</v>
           </cell>
         </row>
         <row r="11">
@@ -629,7 +629,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>308454</v>
+            <v>336099</v>
           </cell>
         </row>
       </sheetData>
@@ -637,7 +637,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>40032</v>
+            <v>43677</v>
           </cell>
         </row>
       </sheetData>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>406700</v>
+        <v>438955</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>340405</v>
+        <v>371695</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.20757541191971582</v>
+        <v>-0.13473580803307464</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>308454</v>
+        <v>336099</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-0.13612596237596589</v>
+        <v>-5.8701783178690355E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>40032</v>
+        <v>43677</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.29474218612043085</v>
+        <v>-0.21428571428571427</v>
       </c>
     </row>
   </sheetData>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>37239</v>
+        <v>39757</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.36973851231276972</v>
+        <v>-0.32712194296352715</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>49487</v>
+        <v>51685</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>0.41456094214498057</v>
+        <v>0.47738966384632975</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140EF390-5777-495A-9C2E-3048105A656A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56202D77-1BDA-41B8-A228-B6E4D88046BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>438955</v>
+            <v>479788</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>371695</v>
+            <v>399095</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-5.8701783178690355E-2</v>
+            <v>-3.9489272081084638E-4</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-0.21428571428571427</v>
+            <v>-6.9022602860674548E-2</v>
           </cell>
         </row>
         <row r="7">
@@ -436,7 +436,7 @@
             <v>2340</v>
           </cell>
           <cell r="I7">
-            <v>2134</v>
+            <v>2999</v>
           </cell>
         </row>
         <row r="8">
@@ -459,7 +459,7 @@
             <v>21670</v>
           </cell>
           <cell r="I8">
-            <v>22642</v>
+            <v>24605</v>
           </cell>
         </row>
         <row r="9">
@@ -482,7 +482,7 @@
             <v>2832</v>
           </cell>
           <cell r="I9">
-            <v>2655</v>
+            <v>3098</v>
           </cell>
         </row>
         <row r="10">
@@ -528,7 +528,7 @@
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>6025</v>
+            <v>8018</v>
           </cell>
         </row>
       </sheetData>
@@ -560,7 +560,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>25681</v>
+            <v>34687</v>
           </cell>
         </row>
       </sheetData>
@@ -629,7 +629,7 @@
       <sheetData sheetId="7">
         <row r="88">
           <cell r="AD88">
-            <v>336099</v>
+            <v>356918</v>
           </cell>
         </row>
       </sheetData>
@@ -637,7 +637,7 @@
       <sheetData sheetId="9">
         <row r="39">
           <cell r="G39">
-            <v>43677</v>
+            <v>50258</v>
           </cell>
         </row>
       </sheetData>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>438955</v>
+        <v>479788</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>371695</v>
+        <v>399095</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-0.13473580803307464</v>
+        <v>-7.0951687020164161E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>336099</v>
+        <v>356918</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-5.8701783178690355E-2</v>
+        <v>-3.9489272081084638E-4</v>
       </c>
     </row>
   </sheetData>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>43677</v>
+        <v>50258</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-0.21428571428571427</v>
+        <v>-6.9022602860674548E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1625,7 +1625,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>51685</v>
+        <v>55641</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>0.47738966384632975</v>
+        <v>0.59046992911045049</v>
       </c>
     </row>
   </sheetData>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
-        <v>4789</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-7.4052590873936577E-2</v>
+        <v>0.1788476411446249</v>
       </c>
     </row>
   </sheetData>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>25681</v>
+        <v>34687</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.35549365055463533</v>
+        <v>-0.12947347287055164</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56202D77-1BDA-41B8-A228-B6E4D88046BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25241C08-6B83-4483-BC00-5656E2DFA2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
   </externalReferences>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>479788</v>
+            <v>512614</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>399095</v>
+            <v>421399</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>-3.9489272081084638E-4</v>
+            <v>6.2070974264757363E-2</v>
           </cell>
         </row>
         <row r="9">
@@ -535,7 +535,7 @@
       <sheetData sheetId="9">
         <row r="15">
           <cell r="K15">
-            <v>10493</v>
+            <v>16570</v>
           </cell>
         </row>
       </sheetData>
@@ -560,7 +560,7 @@
             <v>39846</v>
           </cell>
           <cell r="K11">
-            <v>34687</v>
+            <v>37424</v>
           </cell>
         </row>
       </sheetData>
@@ -585,7 +585,7 @@
             <v>45389</v>
           </cell>
           <cell r="K13">
-            <v>27662</v>
+            <v>35313</v>
           </cell>
         </row>
       </sheetData>
@@ -601,6 +601,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="Balance Sapori vs Inventario"/>
       <sheetName val="INFOGRAFIA"/>
       <sheetName val="Balance Vs Ventas"/>
       <sheetName val="Comparativo Sales LT vs MTD Pro"/>
@@ -626,27 +627,28 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
-      <sheetData sheetId="7">
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
         <row r="88">
           <cell r="AD88">
-            <v>356918</v>
+            <v>379222</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9">
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10">
         <row r="39">
           <cell r="G39">
             <v>50258</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
       <sheetData sheetId="12"/>
       <sheetData sheetId="13"/>
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1012,7 +1014,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>479788</v>
+        <v>512614</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1111,7 +1113,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Gelatina!$K$13</f>
-        <v>27662</v>
+        <v>35313</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1138,7 +1140,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.39055718345854723</v>
+        <v>-0.22199211262640728</v>
       </c>
     </row>
   </sheetData>
@@ -1214,7 +1216,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>399095</v>
+        <v>421399</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1244,7 +1246,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-7.0951687020164161E-2</v>
+        <v>-1.9030481360603761E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1320,7 +1322,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>356918</v>
+        <v>379222</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1347,7 +1349,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>-3.9489272081084638E-4</v>
+        <v>6.2070974264757363E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1831,7 +1833,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Frutas!$K$15</f>
-        <v>10493</v>
+        <v>16570</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1934,7 +1936,7 @@
       </c>
       <c r="G3" s="2">
         <f>[1]Cremosillo!$K$11</f>
-        <v>34687</v>
+        <v>37424</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1961,7 +1963,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12947347287055164</v>
+        <v>-6.0784018471113789E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25241C08-6B83-4483-BC00-5656E2DFA2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BB013B-C858-44C7-A325-A102FDF096AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>512614</v>
+            <v>540206</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>421399</v>
+            <v>448596</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>6.2070974264757363E-2</v>
+            <v>0.13372299815996797</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-6.9022602860674548E-2</v>
+            <v>-3.3418682677026308E-2</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>39757</v>
+            <v>45134</v>
           </cell>
         </row>
       </sheetData>
@@ -505,7 +505,7 @@
             <v>5096</v>
           </cell>
           <cell r="I10">
-            <v>7837</v>
+            <v>12002</v>
           </cell>
         </row>
         <row r="11">
@@ -631,7 +631,7 @@
       <sheetData sheetId="8">
         <row r="88">
           <cell r="AD88">
-            <v>379222</v>
+            <v>404806</v>
           </cell>
         </row>
       </sheetData>
@@ -639,7 +639,7 @@
       <sheetData sheetId="10">
         <row r="39">
           <cell r="G39">
-            <v>50258</v>
+            <v>55503</v>
           </cell>
         </row>
       </sheetData>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>512614</v>
+        <v>540206</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>421399</v>
+        <v>448596</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>-1.9030481360603761E-2</v>
+        <v>4.4281078463780398E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>379222</v>
+        <v>404806</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>6.2070974264757363E-2</v>
+        <v>0.13372299815996797</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>50258</v>
+        <v>55503</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-6.9022602860674548E-2</v>
+        <v>-3.3418682677026308E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>39757</v>
+        <v>45134</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.32712194296352715</v>
+        <v>-0.23611745789963612</v>
       </c>
     </row>
   </sheetData>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>55641</v>
+        <v>59806</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>0.59046992911045049</v>
+        <v>0.7095243539903956</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BB013B-C858-44C7-A325-A102FDF096AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDE057A-6137-4C52-A117-55BD72522D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -205,7 +205,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="J12">
-            <v>540206</v>
+            <v>578361</v>
           </cell>
         </row>
       </sheetData>
@@ -270,7 +270,7 @@
             <v>429574</v>
           </cell>
           <cell r="V9">
-            <v>448596</v>
+            <v>482872</v>
           </cell>
         </row>
         <row r="10">
@@ -312,7 +312,7 @@
             <v>-0.22600580941645712</v>
           </cell>
           <cell r="K7">
-            <v>0.13372299815996797</v>
+            <v>0.22641356190433515</v>
           </cell>
         </row>
         <row r="9">
@@ -346,7 +346,7 @@
             <v>0.38922449480236732</v>
           </cell>
           <cell r="K5">
-            <v>-3.3418682677026308E-2</v>
+            <v>-7.372417446583083E-3</v>
           </cell>
         </row>
         <row r="7">
@@ -388,7 +388,7 @@
             <v>59085</v>
           </cell>
           <cell r="J10">
-            <v>45134</v>
+            <v>60005</v>
           </cell>
         </row>
       </sheetData>
@@ -528,7 +528,7 @@
             <v>0</v>
           </cell>
           <cell r="I11">
-            <v>8018</v>
+            <v>12086</v>
           </cell>
         </row>
       </sheetData>
@@ -631,7 +631,7 @@
       <sheetData sheetId="8">
         <row r="88">
           <cell r="AD88">
-            <v>404806</v>
+            <v>437902</v>
           </cell>
         </row>
       </sheetData>
@@ -639,7 +639,7 @@
       <sheetData sheetId="10">
         <row r="39">
           <cell r="G39">
-            <v>55503</v>
+            <v>60829</v>
           </cell>
         </row>
       </sheetData>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G3" s="9">
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
-        <v>540206</v>
+        <v>578361</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G3" s="6">
         <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>448596</v>
+        <v>482872</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>4.4281078463780398E-2</v>
+        <v>0.1240717548082519</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
-        <v>404806</v>
+        <v>437902</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
-        <v>0.13372299815996797</v>
+        <v>0.22641356190433515</v>
       </c>
     </row>
   </sheetData>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G3" s="11">
         <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>55503</v>
+        <v>60829</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
-        <v>-3.3418682677026308E-2</v>
+        <v>-7.372417446583083E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G3" s="2">
         <f>'[1]Linea Azul'!$J$10</f>
-        <v>45134</v>
+        <v>60005</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.23611745789963612</v>
+        <v>1.557078784801557E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="G3" s="2">
         <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>59806</v>
+        <v>63874</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>0.7095243539903956</v>
+        <v>0.82580608278069978</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEDE057A-6137-4C52-A117-55BD72522D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C878C9-CBE3-436B-91AA-0B48CEB21E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion Total Mensual" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,7 @@
   <externalReferences>
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
+    <externalReference r:id="rId13"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -132,7 +133,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -149,9 +150,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -269,9 +267,6 @@
           <cell r="U9">
             <v>429574</v>
           </cell>
-          <cell r="V9">
-            <v>482872</v>
-          </cell>
         </row>
         <row r="10">
           <cell r="P10">
@@ -412,9 +407,6 @@
           <cell r="H6">
             <v>8218</v>
           </cell>
-          <cell r="I6">
-            <v>15181</v>
-          </cell>
         </row>
         <row r="7">
           <cell r="C7">
@@ -458,9 +450,6 @@
           <cell r="H8">
             <v>21670</v>
           </cell>
-          <cell r="I8">
-            <v>24605</v>
-          </cell>
         </row>
         <row r="9">
           <cell r="C9">
@@ -504,9 +493,6 @@
           <cell r="H10">
             <v>5096</v>
           </cell>
-          <cell r="I10">
-            <v>12002</v>
-          </cell>
         </row>
         <row r="11">
           <cell r="C11">
@@ -526,9 +512,6 @@
           </cell>
           <cell r="H11">
             <v>0</v>
-          </cell>
-          <cell r="I11">
-            <v>12086</v>
           </cell>
         </row>
       </sheetData>
@@ -621,8 +604,20 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1">
+        <row r="4">
+          <cell r="D4">
+            <v>37424</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2">
+        <row r="24">
+          <cell r="C24">
+            <v>76012</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
@@ -649,6 +644,178 @@
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sapori Pruccion Mensual"/>
+      <sheetName val="Comparativo vs Forecast"/>
+      <sheetName val="Total Unidades Mensuales"/>
+      <sheetName val="Total Cremigurt Unidades"/>
+      <sheetName val="150 gr"/>
+      <sheetName val="Hoja3"/>
+      <sheetName val="700 gr"/>
+      <sheetName val="Linea Azul"/>
+      <sheetName val="POWER"/>
+      <sheetName val="Frutas"/>
+      <sheetName val="Cremosillo"/>
+      <sheetName val="Gelatina"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="12">
+          <cell r="K12">
+            <v>80002</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="9">
+          <cell r="V9">
+            <v>500217</v>
+          </cell>
+          <cell r="W9">
+            <v>56225</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="9">
+          <cell r="L9">
+            <v>56225</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6">
+        <row r="7">
+          <cell r="K7">
+            <v>44970</v>
+          </cell>
+          <cell r="L7">
+            <v>7791</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7">
+        <row r="10">
+          <cell r="K10">
+            <v>162</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="6">
+          <cell r="I6">
+            <v>15181</v>
+          </cell>
+          <cell r="J6">
+            <v>4068</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>24605</v>
+          </cell>
+          <cell r="J8">
+            <v>5962</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="J9">
+            <v>469</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="I10">
+            <v>12002</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="I11">
+            <v>12086</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="I12">
+            <v>7967</v>
+          </cell>
+          <cell r="J12">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="I13">
+            <v>7892</v>
+          </cell>
+          <cell r="J13">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="18">
+          <cell r="E18">
+            <v>222793</v>
+          </cell>
+          <cell r="F18">
+            <v>98244</v>
+          </cell>
+          <cell r="G18">
+            <v>173801</v>
+          </cell>
+          <cell r="H18">
+            <v>192306</v>
+          </cell>
+          <cell r="I18">
+            <v>164217</v>
+          </cell>
+          <cell r="J18">
+            <v>194544</v>
+          </cell>
+          <cell r="K18">
+            <v>239872</v>
+          </cell>
+          <cell r="L18">
+            <v>21861</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10">
+        <row r="11">
+          <cell r="L11">
+            <v>11529</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="13">
+          <cell r="L13">
+            <v>11249</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -951,20 +1118,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A50725-B085-4570-857C-BD64735FAA95}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -986,8 +1153,11 @@
       <c r="G2" s="8">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="8">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>'[1]Total Unidades Mensuales'!I12</f>
         <v>520938</v>
@@ -1016,8 +1186,12 @@
         <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
         <v>578361</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <f>'[3]Sapori Pruccion Mensual'!$K$12</f>
+        <v>80002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <f>'[1]Total Unidades Mensuales'!J13</f>
         <v>-0.2070323147860206</v>
@@ -1038,7 +1212,14 @@
         <f>'[1]Total Unidades Mensuales'!N13</f>
         <v>-0.14833758751159298</v>
       </c>
-      <c r="G4" s="10"/>
+      <c r="G4" s="3">
+        <f>(G3-F3)/F3</f>
+        <v>0.11472581947702265</v>
+      </c>
+      <c r="H4" s="3">
+        <f>(H3-G3)/G3</f>
+        <v>-0.86167462882179124</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1050,20 +1231,20 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F921FD-1DF5-467A-8795-A0197415D027}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1085,8 +1266,11 @@
       <c r="G2" s="5">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>[1]Gelatina!E13</f>
         <v>18271</v>
@@ -1115,8 +1299,12 @@
         <f>[1]Gelatina!$K$13</f>
         <v>35313</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <f>[3]Gelatina!$L$13</f>
+        <v>11249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
         <f>(B3-A3)/A3</f>
@@ -1127,7 +1315,7 @@
         <v>0.66149620294070122</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:G4" si="0">(D3-C3)/C3</f>
+        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>-2.5738273525884144E-2</v>
       </c>
       <c r="E4" s="4">
@@ -1141,6 +1329,10 @@
       <c r="G4" s="4">
         <f t="shared" si="0"/>
         <v>-0.22199211262640728</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.68144875824767082</v>
       </c>
     </row>
   </sheetData>
@@ -1153,20 +1345,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921C7DED-5639-47E9-9129-9ED451DB0330}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1188,8 +1380,11 @@
       <c r="G2" s="5">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>'[1]Total Cremigurt Unidades'!P9</f>
         <v>466290</v>
@@ -1215,11 +1410,15 @@
         <v>429574</v>
       </c>
       <c r="G3" s="6">
-        <f>'[1]Total Cremigurt Unidades'!$V$9</f>
-        <v>482872</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <f>'[3]Total Cremigurt Unidades'!$V$9</f>
+        <v>500217</v>
+      </c>
+      <c r="H3" s="2">
+        <f>'[3]Total Cremigurt Unidades'!$W$9</f>
+        <v>56225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>'[1]Total Cremigurt Unidades'!P10</f>
         <v>0.47828650777044379</v>
@@ -1246,7 +1445,11 @@
       </c>
       <c r="G4" s="7">
         <f>(G3-F3)/F3</f>
-        <v>0.1240717548082519</v>
+        <v>0.16444896571952677</v>
+      </c>
+      <c r="H4" s="7">
+        <f>(H3-G3)/G3</f>
+        <v>-0.88759878212855625</v>
       </c>
     </row>
   </sheetData>
@@ -1259,20 +1462,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53811579-B0AE-4BBF-B8B9-801ECC475242}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1294,8 +1497,11 @@
       <c r="G2" s="5">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>'[1]150 gr'!E9</f>
         <v>386904</v>
@@ -1320,12 +1526,16 @@
         <f>'[1]150 gr'!J9</f>
         <v>357059</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="10">
         <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
         <v>437902</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <f>'[3]150 gr'!$L$9</f>
+        <v>56225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
         <f>'[1]150 gr'!F7</f>
@@ -1350,6 +1560,10 @@
       <c r="G4" s="3">
         <f>'[1]150 gr'!K7</f>
         <v>0.22641356190433515</v>
+      </c>
+      <c r="H4" s="7">
+        <f>(H3-G3)/G3</f>
+        <v>-0.87160369215029843</v>
       </c>
     </row>
   </sheetData>
@@ -1362,20 +1576,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F86516D-CC49-45A3-8161-FD9764305B52}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1397,8 +1611,11 @@
       <c r="G2" s="5">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>'[1]700 gr'!E7</f>
         <v>43534</v>
@@ -1423,12 +1640,16 @@
         <f>'[1]700 gr'!J7</f>
         <v>45304</v>
       </c>
-      <c r="G3" s="11">
-        <f>'[2]Produccion MTD SHARE'!$G$39</f>
-        <v>60829</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G3" s="10">
+        <f>'[3]700 gr'!$K$7</f>
+        <v>44970</v>
+      </c>
+      <c r="H3" s="2">
+        <f>'[3]700 gr'!$L$7</f>
+        <v>7791</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
         <f>'[1]700 gr'!F5</f>
@@ -1453,6 +1674,10 @@
       <c r="G4" s="3">
         <f>'[1]700 gr'!K5</f>
         <v>-7.372417446583083E-3</v>
+      </c>
+      <c r="H4" s="7">
+        <f>(H3-G3)/G3</f>
+        <v>-0.82675116744496335</v>
       </c>
     </row>
   </sheetData>
@@ -1465,20 +1690,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50800131-7A3A-4EA9-BC89-BE76C1CC5304}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1500,8 +1725,11 @@
       <c r="G2" s="5">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1529,8 +1757,12 @@
         <f>'[1]Linea Azul'!$J$10</f>
         <v>60005</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <f>'[3]Linea Azul'!$K$10</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4">
@@ -1538,7 +1770,7 @@
         <v>1.4046501312238939</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:G4" si="0">(D3-C3)/C3</f>
+        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>8.5315050804728454E-3</v>
       </c>
       <c r="E4" s="4">
@@ -1552,6 +1784,10 @@
       <c r="G4" s="4">
         <f t="shared" si="0"/>
         <v>1.557078784801557E-2</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.99730022498125159</v>
       </c>
     </row>
   </sheetData>
@@ -1564,20 +1800,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA85D05B-3ECD-40A5-BED5-A9D687E905B1}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1596,11 +1832,14 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="11">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>[1]POWER!$C$6+[1]POWER!$C$8+[1]POWER!$C$10+[1]POWER!$C$11</f>
         <v>87654</v>
@@ -1626,11 +1865,15 @@
         <v>34984</v>
       </c>
       <c r="G3" s="2">
-        <f>+[1]POWER!$I$6+[1]POWER!$I$8+[1]POWER!$I$10+[1]POWER!$I$11</f>
-        <v>63874</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <f>[3]POWER!$I$6+[3]POWER!$I$8+[3]POWER!$I$10+[3]POWER!$I$11+[3]POWER!$I$12+[3]POWER!$I$13</f>
+        <v>79733</v>
+      </c>
+      <c r="H3" s="2">
+        <f>[3]POWER!$J$6+[3]POWER!$J$8+[3]POWER!$J$10+[3]POWER!$J$11+[3]POWER!$J$12+[3]POWER!$J$13</f>
+        <v>10030</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
         <f>(B3-A3)/A3</f>
@@ -1641,7 +1884,7 @@
         <v>0.10021089581180734</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:G4" si="0">(D3-C3)/C3</f>
+        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>-0.12225495619508304</v>
       </c>
       <c r="E4" s="4">
@@ -1654,7 +1897,11 @@
       </c>
       <c r="G4" s="4">
         <f t="shared" si="0"/>
-        <v>0.82580608278069978</v>
+        <v>1.2791276011891151</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.87420515972056745</v>
       </c>
     </row>
   </sheetData>
@@ -1667,20 +1914,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04414C49-388F-40D7-B11A-32B8FBF66B8E}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1699,11 +1946,14 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="11">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>[1]POWER!$C$7+[1]POWER!$C$9</f>
         <v>5176</v>
@@ -1732,8 +1982,12 @@
         <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
         <v>6097</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <f>[3]POWER!$J$7+[3]POWER!$J$9</f>
+        <v>469</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
         <f>(B3-A3)/A3</f>
@@ -1744,7 +1998,7 @@
         <v>-5.008347245409015E-3</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:G4" si="0">(D3-C3)/C3</f>
+        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>7.0469798657718116E-2</v>
       </c>
       <c r="E4" s="4">
@@ -1758,6 +2012,10 @@
       <c r="G4" s="4">
         <f t="shared" si="0"/>
         <v>0.1788476411446249</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.92307692307692313</v>
       </c>
     </row>
   </sheetData>
@@ -1770,20 +2028,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1607DE2-0B78-461F-9558-D9AD76E0CDAB}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1802,65 +2060,76 @@
       <c r="F2" s="1">
         <v>46204</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="11">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>[1]Frutas!E15</f>
-        <v>0</v>
+        <f>[3]Frutas!$E$18</f>
+        <v>222793</v>
       </c>
       <c r="B3" s="2">
-        <f>[1]Frutas!F15</f>
-        <v>0</v>
+        <f>[3]Frutas!$F$18</f>
+        <v>98244</v>
       </c>
       <c r="C3" s="2">
-        <f>[1]Frutas!G15</f>
-        <v>0</v>
+        <f>[3]Frutas!$G$18</f>
+        <v>173801</v>
       </c>
       <c r="D3" s="2">
-        <f>[1]Frutas!H15</f>
-        <v>0</v>
+        <f>[3]Frutas!$H$18</f>
+        <v>192306</v>
       </c>
       <c r="E3" s="2">
-        <f>[1]Frutas!I15</f>
-        <v>0</v>
+        <f>[3]Frutas!$I$18</f>
+        <v>164217</v>
       </c>
       <c r="F3" s="2">
-        <f>[1]Frutas!J15</f>
-        <v>0</v>
+        <f>[3]Frutas!$J$18</f>
+        <v>194544</v>
       </c>
       <c r="G3" s="2">
-        <f>[1]Frutas!$K$15</f>
-        <v>16570</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <f>[3]Frutas!$K$18</f>
+        <v>239872</v>
+      </c>
+      <c r="H3" s="2">
+        <f>[3]Frutas!$L$18</f>
+        <v>21861</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
-      <c r="B4" s="4" t="e">
+      <c r="B4" s="4">
         <f>(B3-A3)/A3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C4" s="4" t="e">
+        <v>-0.55903461957960976</v>
+      </c>
+      <c r="C4" s="4">
         <f>(C3-B3)/B3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D4" s="4" t="e">
-        <f t="shared" ref="D4:G4" si="0">(D3-C3)/C3</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E4" s="4" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F4" s="4" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G4" s="4" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
+        <v>0.76907495623142386</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
+        <v>0.10647234480814265</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.14606408536395121</v>
+      </c>
+      <c r="F4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.18467637333528197</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.23299613455053869</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.90886389407684098</v>
       </c>
     </row>
   </sheetData>
@@ -1873,20 +2142,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76579A32-DE1B-43F8-A9E1-7A0C474A6180}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1908,8 +2177,11 @@
       <c r="G2" s="5">
         <v>46235</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="5">
+        <v>46266</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>[1]Cremosillo!E11</f>
         <v>19349</v>
@@ -1938,8 +2210,12 @@
         <f>[1]Cremosillo!$K$11</f>
         <v>37424</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" s="2">
+        <f>[3]Cremosillo!$L$11</f>
+        <v>11529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
         <f>(B3-A3)/A3</f>
@@ -1950,7 +2226,7 @@
         <v>-7.6457095806622355E-2</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:G4" si="0">(D3-C3)/C3</f>
+        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>0.58835891230974968</v>
       </c>
       <c r="E4" s="4">
@@ -1964,6 +2240,10 @@
       <c r="G4" s="4">
         <f t="shared" si="0"/>
         <v>-6.0784018471113789E-2</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="0"/>
+        <v>-0.6919356562633604</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C878C9-CBE3-436B-91AA-0B48CEB21E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58D6484-433A-4041-89B1-AFACD84F0E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="9" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
   <sheets>
     <sheet name="Produccion Total Mensual" sheetId="1" r:id="rId1"/>
@@ -584,6 +584,178 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
+      <sheetName val="Sapori Pruccion Mensual"/>
+      <sheetName val="Comparativo vs Forecast"/>
+      <sheetName val="Total Unidades Mensuales"/>
+      <sheetName val="Total Cremigurt Unidades"/>
+      <sheetName val="150 gr"/>
+      <sheetName val="Hoja3"/>
+      <sheetName val="700 gr"/>
+      <sheetName val="Linea Azul"/>
+      <sheetName val="POWER"/>
+      <sheetName val="Frutas"/>
+      <sheetName val="Cremosillo"/>
+      <sheetName val="Gelatina"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="12">
+          <cell r="K12">
+            <v>109252</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="9">
+          <cell r="V9">
+            <v>500217</v>
+          </cell>
+          <cell r="W9">
+            <v>84912</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4">
+        <row r="9">
+          <cell r="L9">
+            <v>84912</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6">
+        <row r="7">
+          <cell r="K7">
+            <v>44970</v>
+          </cell>
+          <cell r="L7">
+            <v>8684</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="7">
+        <row r="10">
+          <cell r="K10">
+            <v>10067</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="8">
+        <row r="6">
+          <cell r="I6">
+            <v>15181</v>
+          </cell>
+          <cell r="J6">
+            <v>4068</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>880</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="I8">
+            <v>24605</v>
+          </cell>
+          <cell r="J8">
+            <v>5962</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="J9">
+            <v>469</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="I10">
+            <v>12002</v>
+          </cell>
+          <cell r="J10">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="I11">
+            <v>12086</v>
+          </cell>
+          <cell r="J11">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="I12">
+            <v>7967</v>
+          </cell>
+          <cell r="J12">
+            <v>4094</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="I13">
+            <v>7892</v>
+          </cell>
+          <cell r="J13">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="9">
+        <row r="18">
+          <cell r="E18">
+            <v>222793</v>
+          </cell>
+          <cell r="F18">
+            <v>98244</v>
+          </cell>
+          <cell r="G18">
+            <v>173801</v>
+          </cell>
+          <cell r="H18">
+            <v>192306</v>
+          </cell>
+          <cell r="I18">
+            <v>164217</v>
+          </cell>
+          <cell r="J18">
+            <v>194544</v>
+          </cell>
+          <cell r="K18">
+            <v>239872</v>
+          </cell>
+          <cell r="L18">
+            <v>33160</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="10">
+        <row r="11">
+          <cell r="L11">
+            <v>11529</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="11">
+        <row r="13">
+          <cell r="L13">
+            <v>11249</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
       <sheetName val="Balance Sapori vs Inventario"/>
       <sheetName val="INFOGRAFIA"/>
       <sheetName val="Balance Vs Ventas"/>
@@ -644,178 +816,6 @@
       <sheetData sheetId="14"/>
       <sheetData sheetId="15"/>
       <sheetData sheetId="16"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sapori Pruccion Mensual"/>
-      <sheetName val="Comparativo vs Forecast"/>
-      <sheetName val="Total Unidades Mensuales"/>
-      <sheetName val="Total Cremigurt Unidades"/>
-      <sheetName val="150 gr"/>
-      <sheetName val="Hoja3"/>
-      <sheetName val="700 gr"/>
-      <sheetName val="Linea Azul"/>
-      <sheetName val="POWER"/>
-      <sheetName val="Frutas"/>
-      <sheetName val="Cremosillo"/>
-      <sheetName val="Gelatina"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="12">
-          <cell r="K12">
-            <v>80002</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="9">
-          <cell r="V9">
-            <v>500217</v>
-          </cell>
-          <cell r="W9">
-            <v>56225</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="9">
-          <cell r="L9">
-            <v>56225</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6">
-        <row r="7">
-          <cell r="K7">
-            <v>44970</v>
-          </cell>
-          <cell r="L7">
-            <v>7791</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="10">
-          <cell r="K10">
-            <v>162</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8">
-        <row r="6">
-          <cell r="I6">
-            <v>15181</v>
-          </cell>
-          <cell r="J6">
-            <v>4068</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="I8">
-            <v>24605</v>
-          </cell>
-          <cell r="J8">
-            <v>5962</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="J9">
-            <v>469</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="I10">
-            <v>12002</v>
-          </cell>
-          <cell r="J10">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="I11">
-            <v>12086</v>
-          </cell>
-          <cell r="J11">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="I12">
-            <v>7967</v>
-          </cell>
-          <cell r="J12">
-            <v>0</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="I13">
-            <v>7892</v>
-          </cell>
-          <cell r="J13">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9">
-        <row r="18">
-          <cell r="E18">
-            <v>222793</v>
-          </cell>
-          <cell r="F18">
-            <v>98244</v>
-          </cell>
-          <cell r="G18">
-            <v>173801</v>
-          </cell>
-          <cell r="H18">
-            <v>192306</v>
-          </cell>
-          <cell r="I18">
-            <v>164217</v>
-          </cell>
-          <cell r="J18">
-            <v>194544</v>
-          </cell>
-          <cell r="K18">
-            <v>239872</v>
-          </cell>
-          <cell r="L18">
-            <v>21861</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10">
-        <row r="11">
-          <cell r="L11">
-            <v>11529</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11">
-        <row r="13">
-          <cell r="L13">
-            <v>11249</v>
-          </cell>
-        </row>
-      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1187,8 +1187,8 @@
         <v>578361</v>
       </c>
       <c r="H3" s="2">
-        <f>'[3]Sapori Pruccion Mensual'!$K$12</f>
-        <v>80002</v>
+        <f>'[2]Sapori Pruccion Mensual'!$K$12</f>
+        <v>109252</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.86167462882179124</v>
+        <v>-0.81110067933349583</v>
       </c>
     </row>
   </sheetData>
@@ -1300,7 +1300,7 @@
         <v>35313</v>
       </c>
       <c r="H3" s="2">
-        <f>[3]Gelatina!$L$13</f>
+        <f>[2]Gelatina!$L$13</f>
         <v>11249</v>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
         <v>429574</v>
       </c>
       <c r="G3" s="6">
-        <f>'[3]Total Cremigurt Unidades'!$V$9</f>
+        <f>'[2]Total Cremigurt Unidades'!$V$9</f>
         <v>500217</v>
       </c>
       <c r="H3" s="2">
-        <f>'[3]Total Cremigurt Unidades'!$W$9</f>
-        <v>56225</v>
+        <f>'[2]Total Cremigurt Unidades'!$W$9</f>
+        <v>84912</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.88759878212855625</v>
+        <v>-0.83024967164250718</v>
       </c>
     </row>
   </sheetData>
@@ -1527,12 +1527,12 @@
         <v>357059</v>
       </c>
       <c r="G3" s="10">
-        <f>'[2]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
+        <f>'[3]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
         <v>437902</v>
       </c>
       <c r="H3" s="2">
-        <f>'[3]150 gr'!$L$9</f>
-        <v>56225</v>
+        <f>'[2]150 gr'!$L$9</f>
+        <v>84912</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.87160369215029843</v>
+        <v>-0.80609360085133208</v>
       </c>
     </row>
   </sheetData>
@@ -1641,12 +1641,12 @@
         <v>45304</v>
       </c>
       <c r="G3" s="10">
-        <f>'[3]700 gr'!$K$7</f>
+        <f>'[2]700 gr'!$K$7</f>
         <v>44970</v>
       </c>
       <c r="H3" s="2">
-        <f>'[3]700 gr'!$L$7</f>
-        <v>7791</v>
+        <f>'[2]700 gr'!$L$7</f>
+        <v>8684</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.82675116744496335</v>
+        <v>-0.80689348454525234</v>
       </c>
     </row>
   </sheetData>
@@ -1758,8 +1758,8 @@
         <v>60005</v>
       </c>
       <c r="H3" s="2">
-        <f>'[3]Linea Azul'!$K$10</f>
-        <v>162</v>
+        <f>'[2]Linea Azul'!$K$10</f>
+        <v>10067</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.99730022498125159</v>
+        <v>-0.83223064744604613</v>
       </c>
     </row>
   </sheetData>
@@ -1865,12 +1865,12 @@
         <v>34984</v>
       </c>
       <c r="G3" s="2">
-        <f>[3]POWER!$I$6+[3]POWER!$I$8+[3]POWER!$I$10+[3]POWER!$I$11+[3]POWER!$I$12+[3]POWER!$I$13</f>
+        <f>[2]POWER!$I$6+[2]POWER!$I$8+[2]POWER!$I$10+[2]POWER!$I$11+[2]POWER!$I$12+[2]POWER!$I$13</f>
         <v>79733</v>
       </c>
       <c r="H3" s="2">
-        <f>[3]POWER!$J$6+[3]POWER!$J$8+[3]POWER!$J$10+[3]POWER!$J$11+[3]POWER!$J$12+[3]POWER!$J$13</f>
-        <v>10030</v>
+        <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
+        <v>14124</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.87420515972056745</v>
+        <v>-0.82285879121568239</v>
       </c>
     </row>
   </sheetData>
@@ -1983,8 +1983,8 @@
         <v>6097</v>
       </c>
       <c r="H3" s="2">
-        <f>[3]POWER!$J$7+[3]POWER!$J$9</f>
-        <v>469</v>
+        <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
+        <v>1349</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.92307692307692313</v>
+        <v>-0.77874364441528621</v>
       </c>
     </row>
   </sheetData>
@@ -2069,36 +2069,36 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>[3]Frutas!$E$18</f>
+        <f>[2]Frutas!$E$18</f>
         <v>222793</v>
       </c>
       <c r="B3" s="2">
-        <f>[3]Frutas!$F$18</f>
+        <f>[2]Frutas!$F$18</f>
         <v>98244</v>
       </c>
       <c r="C3" s="2">
-        <f>[3]Frutas!$G$18</f>
+        <f>[2]Frutas!$G$18</f>
         <v>173801</v>
       </c>
       <c r="D3" s="2">
-        <f>[3]Frutas!$H$18</f>
+        <f>[2]Frutas!$H$18</f>
         <v>192306</v>
       </c>
       <c r="E3" s="2">
-        <f>[3]Frutas!$I$18</f>
+        <f>[2]Frutas!$I$18</f>
         <v>164217</v>
       </c>
       <c r="F3" s="2">
-        <f>[3]Frutas!$J$18</f>
+        <f>[2]Frutas!$J$18</f>
         <v>194544</v>
       </c>
       <c r="G3" s="2">
-        <f>[3]Frutas!$K$18</f>
+        <f>[2]Frutas!$K$18</f>
         <v>239872</v>
       </c>
       <c r="H3" s="2">
-        <f>[3]Frutas!$L$18</f>
-        <v>21861</v>
+        <f>[2]Frutas!$L$18</f>
+        <v>33160</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.90886389407684098</v>
+        <v>-0.86175960512273209</v>
       </c>
     </row>
   </sheetData>
@@ -2211,7 +2211,7 @@
         <v>37424</v>
       </c>
       <c r="H3" s="2">
-        <f>[3]Cremosillo!$L$11</f>
+        <f>[2]Cremosillo!$L$11</f>
         <v>11529</v>
       </c>
     </row>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58D6484-433A-4041-89B1-AFACD84F0E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C07C49-CA1B-4C16-9F6D-354DB5237B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -601,7 +601,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="K12">
-            <v>109252</v>
+            <v>139177</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>84912</v>
+            <v>111079</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>84912</v>
+            <v>111079</v>
           </cell>
         </row>
       </sheetData>
@@ -631,7 +631,7 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>8684</v>
+            <v>12862</v>
           </cell>
         </row>
       </sheetData>
@@ -648,7 +648,7 @@
             <v>15181</v>
           </cell>
           <cell r="J6">
-            <v>4068</v>
+            <v>5266</v>
           </cell>
         </row>
         <row r="7">
@@ -661,12 +661,12 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>5962</v>
+            <v>8698</v>
           </cell>
         </row>
         <row r="9">
           <cell r="J9">
-            <v>469</v>
+            <v>1374</v>
           </cell>
         </row>
         <row r="10">
@@ -698,7 +698,7 @@
             <v>7892</v>
           </cell>
           <cell r="J13">
-            <v>0</v>
+            <v>4163</v>
           </cell>
         </row>
       </sheetData>
@@ -726,14 +726,14 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>33160</v>
+            <v>49556</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>11529</v>
+            <v>15287</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Sapori Pruccion Mensual'!$K$12</f>
-        <v>109252</v>
+        <v>139177</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.81110067933349583</v>
+        <v>-0.75935963870316292</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>84912</v>
+        <v>111079</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.83024967164250718</v>
+        <v>-0.77793837474536054</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>84912</v>
+        <v>111079</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.80609360085133208</v>
+        <v>-0.7463382217939174</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>8684</v>
+        <v>12862</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.80689348454525234</v>
+        <v>-0.7139871025127863</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>14124</v>
+        <v>22221</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.82285879121568239</v>
+        <v>-0.72130736332509748</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>1349</v>
+        <v>2254</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.77874364441528621</v>
+        <v>-0.63030998851894371</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>33160</v>
+        <v>49556</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.86175960512273209</v>
+        <v>-0.79340648345784415</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>11529</v>
+        <v>15287</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.6919356562633604</v>
+        <v>-0.59151881145788798</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C07C49-CA1B-4C16-9F6D-354DB5237B4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9B5F5C-E5D1-4CCE-BB35-D7032502092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -601,7 +601,7 @@
       <sheetData sheetId="0">
         <row r="12">
           <cell r="K12">
-            <v>139177</v>
+            <v>174148</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>111079</v>
+            <v>137146</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>111079</v>
+            <v>137146</v>
           </cell>
         </row>
       </sheetData>
@@ -726,21 +726,21 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>49556</v>
+            <v>73166</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>15287</v>
+            <v>18263</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>11249</v>
+            <v>17177</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Sapori Pruccion Mensual'!$K$12</f>
-        <v>139177</v>
+        <v>174148</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.75935963870316292</v>
+        <v>-0.69889394340213118</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>11249</v>
+        <v>17177</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.68144875824767082</v>
+        <v>-0.51357856879902586</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>111079</v>
+        <v>137146</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.77793837474536054</v>
+        <v>-0.72582699108586868</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>111079</v>
+        <v>137146</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.7463382217939174</v>
+        <v>-0.68681120433338971</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>49556</v>
+        <v>73166</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.79340648345784415</v>
+        <v>-0.69497898879402353</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>15287</v>
+        <v>18263</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.59151881145788798</v>
+        <v>-0.51199764856776397</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C9B5F5C-E5D1-4CCE-BB35-D7032502092D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3B696E-3D54-4B7E-93F6-C26769D1F7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -584,7 +584,7 @@
       <xxl21:absoluteUrl r:id="rId2"/>
     </xxl21:alternateUrls>
     <sheetNames>
-      <sheetName val="Sapori Pruccion Mensual"/>
+      <sheetName val="Sapori Produccion Mensual"/>
       <sheetName val="Comparativo vs Forecast"/>
       <sheetName val="Total Unidades Mensuales"/>
       <sheetName val="Total Cremigurt Unidades"/>
@@ -598,29 +598,29 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
         <row r="12">
-          <cell r="K12">
-            <v>174148</v>
+          <cell r="P12">
+            <v>209431</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
       <sheetData sheetId="3">
         <row r="9">
           <cell r="V9">
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>137146</v>
+            <v>169022</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>137146</v>
+            <v>169022</v>
           </cell>
         </row>
       </sheetData>
@@ -631,14 +631,14 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>12862</v>
+            <v>14397</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>10067</v>
+            <v>19921</v>
           </cell>
         </row>
       </sheetData>
@@ -674,7 +674,7 @@
             <v>12002</v>
           </cell>
           <cell r="J10">
-            <v>0</v>
+            <v>2003</v>
           </cell>
         </row>
         <row r="11">
@@ -682,7 +682,7 @@
             <v>12086</v>
           </cell>
           <cell r="J11">
-            <v>0</v>
+            <v>1931</v>
           </cell>
         </row>
         <row r="12">
@@ -740,7 +740,7 @@
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>17177</v>
+            <v>20584</v>
           </cell>
         </row>
       </sheetData>
@@ -1187,8 +1187,8 @@
         <v>578361</v>
       </c>
       <c r="H3" s="2">
-        <f>'[2]Sapori Pruccion Mensual'!$K$12</f>
-        <v>174148</v>
+        <f>'[2]Total Unidades Mensuales'!$P$12</f>
+        <v>209431</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.69889394340213118</v>
+        <v>-0.63788879263989096</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>17177</v>
+        <v>20584</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.51357856879902586</v>
+        <v>-0.41709851895902361</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>137146</v>
+        <v>169022</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.72582699108586868</v>
+        <v>-0.66210264745100622</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>137146</v>
+        <v>169022</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.68681120433338971</v>
+        <v>-0.61401866170969766</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>12862</v>
+        <v>14397</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.7139871025127863</v>
+        <v>-0.67985323549032683</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>10067</v>
+        <v>19921</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.83223064744604613</v>
+        <v>-0.66801099908340966</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>22221</v>
+        <v>26155</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.72130736332509748</v>
+        <v>-0.67196769217262609</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3B696E-3D54-4B7E-93F6-C26769D1F7F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9C5599-E710-4D06-B17C-2CA9F5D834FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>209431</v>
+            <v>233564</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>169022</v>
+            <v>192392</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>169022</v>
+            <v>192392</v>
           </cell>
         </row>
       </sheetData>
@@ -631,7 +631,7 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>14397</v>
+            <v>17946</v>
           </cell>
         </row>
       </sheetData>
@@ -648,7 +648,7 @@
             <v>15181</v>
           </cell>
           <cell r="J6">
-            <v>5266</v>
+            <v>7187</v>
           </cell>
         </row>
         <row r="7">
@@ -661,7 +661,7 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>8698</v>
+            <v>12962</v>
           </cell>
         </row>
         <row r="9">
@@ -726,7 +726,7 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>73166</v>
+            <v>81812</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>209431</v>
+        <v>233564</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.63788879263989096</v>
+        <v>-0.59616225852019755</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>169022</v>
+        <v>192392</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.66210264745100622</v>
+        <v>-0.61538292381106596</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>169022</v>
+        <v>192392</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.61401866170969766</v>
+        <v>-0.56065055651721163</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>14397</v>
+        <v>17946</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.67985323549032683</v>
+        <v>-0.60093395597064714</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>26155</v>
+        <v>32340</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.67196769217262609</v>
+        <v>-0.59439629764338475</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>73166</v>
+        <v>81812</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.69497898879402353</v>
+        <v>-0.65893476520811101</v>
       </c>
     </row>
   </sheetData>
